--- a/winner_final/data/wnba.xlsx
+++ b/winner_final/data/wnba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkdk1\PycharmProjects\PythonProjectNew\winner_final\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62252A8C-C8AD-4F80-B72F-25E530F12D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184653BE-3320-4EC6-B107-85C5741D1135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="-11430" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="888" yWindow="1500" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>Atlanta Dream</t>
   </si>
@@ -97,6 +97,24 @@
   </si>
   <si>
     <t>Toronto Tempo</t>
+  </si>
+  <si>
+    <t>גולדן סטייט ולקיריס</t>
+  </si>
+  <si>
+    <t>Golden State Valkyries</t>
+  </si>
+  <si>
+    <t>לאס וגאס אייסז</t>
+  </si>
+  <si>
+    <t>פיניקס מרקורי</t>
+  </si>
+  <si>
+    <t>סיאטל סטורם</t>
+  </si>
+  <si>
+    <t>v</t>
   </si>
 </sst>
 </file>
@@ -146,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -157,6 +175,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,14 +456,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.8984375" customWidth="1"/>
     <col min="2" max="3" width="29.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -455,135 +474,188 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
       <c r="B6" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
       <c r="B10" s="3">
-        <v>17</v>
-      </c>
-      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="B11" s="3">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="B12" s="3">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="3">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="3">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="3">
-        <v>19</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="3">
-        <v>22</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="3">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
+      <c r="D15" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/winner_final/data/wnba.xlsx
+++ b/winner_final/data/wnba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkdk1\PycharmProjects\PythonProjectNew\winner_final\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184653BE-3320-4EC6-B107-85C5741D1135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42180259-563D-4C8C-80B2-B12A4CE3749A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="888" yWindow="1500" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6510" yWindow="-12795" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <si>
     <t>Atlanta Dream</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>v</t>
+  </si>
+  <si>
+    <t>לוס אנג'לס ספארקס</t>
   </si>
 </sst>
 </file>
@@ -456,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.8984375" customWidth="1"/>
@@ -638,7 +641,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="3">
-        <v>19</v>
+        <v>129689</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
@@ -656,6 +659,17 @@
       </c>
       <c r="D15" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/winner_final/data/wnba.xlsx
+++ b/winner_final/data/wnba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkdk1\PycharmProjects\PythonProjectNew\winner_final\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42180259-563D-4C8C-80B2-B12A4CE3749A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE16C62-0AE4-403A-8737-1C0D7B22EF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6510" yWindow="-12795" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1236" yWindow="1608" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>Atlanta Dream</t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <t>לוס אנג'לס ספארקס</t>
+  </si>
+  <si>
+    <t>אטלנטה דרים</t>
+  </si>
+  <si>
+    <t>אינדיאנה פיבר</t>
   </si>
 </sst>
 </file>
@@ -167,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -176,9 +182,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,7 +493,9 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+      <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="B2" s="3">
         <v>20</v>
       </c>
@@ -518,7 +535,9 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="B5" s="3">
         <v>5</v>
       </c>
@@ -530,7 +549,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3">
@@ -584,7 +603,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="3">
@@ -637,7 +656,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="3">
@@ -648,7 +667,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="3">
@@ -662,7 +681,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="3">

--- a/winner_final/data/wnba.xlsx
+++ b/winner_final/data/wnba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkdk1\PycharmProjects\PythonProjectNew\winner_final\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE16C62-0AE4-403A-8737-1C0D7B22EF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C79135-0321-457D-AEFA-0B6068CA6BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1236" yWindow="1608" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1236" yWindow="1008" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>

--- a/winner_final/data/wnba.xlsx
+++ b/winner_final/data/wnba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkdk1\PycharmProjects\PythonProjectNew\winner_final\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C79135-0321-457D-AEFA-0B6068CA6BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC219CDD-FC91-4949-B2C9-6EA7126441F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1236" yWindow="1008" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>Atlanta Dream</t>
   </si>
@@ -124,6 +124,12 @@
   </si>
   <si>
     <t>אינדיאנה פיבר</t>
+  </si>
+  <si>
+    <t>פורטלנד פייר</t>
+  </si>
+  <si>
+    <t>Portland Fire</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.8984375" customWidth="1"/>
@@ -690,6 +696,20 @@
       <c r="C16" t="s">
         <v>5</v>
       </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
